--- a/Peter/Sectoral Analysis (ISIC)/ISIC4/ISIC4_tidied.xlsx
+++ b/Peter/Sectoral Analysis (ISIC)/ISIC4/ISIC4_tidied.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bede7/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bede7/Desktop/RA/rproj-NatlAccountsSectorData/Peter/Sectoral Analysis (ISIC)/ISIC4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AB1A5B-32DF-3B4C-82A4-0CB82B2CE98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{952C5552-444D-D845-B336-D82EA3B4EF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7280" yWindow="820" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -195,9 +195,6 @@
     <t>Trinidad and Tobago dollar</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>Industry</t>
   </si>
   <si>
@@ -205,9 +202,6 @@
   </si>
   <si>
     <t>Transportation</t>
-  </si>
-  <si>
-    <t>Hotel and Resturant</t>
   </si>
   <si>
     <t>Financial</t>
@@ -223,6 +217,12 @@
   </si>
   <si>
     <t>G+J+M+N+R+S+T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary </t>
+  </si>
+  <si>
+    <t>Hospitality</t>
   </si>
 </sst>
 </file>
@@ -585,31 +585,31 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -15559,31 +15559,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -15609,7 +15609,7 @@
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
@@ -15617,5 +15617,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>